--- a/docs/reports/Shelly_Budget_Plan.xlsx
+++ b/docs/reports/Shelly_Budget_Plan.xlsx
@@ -22813,7 +22813,7 @@
     <row r="6">
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 25 Sep 2026.  Shelly v1.1.0.</t>
+          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 25 Sep 2026.  Shelly v1.4.0.</t>
         </is>
       </c>
     </row>
@@ -22984,7 +22984,7 @@
     <row r="28">
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 29 Sep 2026 22:16</t>
+          <t>Generated by Shelly on 03 Oct 2026 05:37</t>
         </is>
       </c>
     </row>

--- a/docs/reports/Shelly_Budget_Plan.xlsx
+++ b/docs/reports/Shelly_Budget_Plan.xlsx
@@ -22984,7 +22984,7 @@
     <row r="28">
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 03 Oct 2026 05:37</t>
+          <t>Generated by Shelly on 03 Oct 2026 05:50</t>
         </is>
       </c>
     </row>
